--- a/Modbus-Register (HY-5K-TL-LV).xlsx
+++ b/Modbus-Register (HY-5K-TL-LV).xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="236">
   <si>
     <t xml:space="preserve">Register</t>
   </si>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">0x405C</t>
   </si>
   <si>
-    <t xml:space="preserve">Ladeschlussspannung?</t>
+    <t xml:space="preserve">Ladeschlussspannung (0x0217=53,5V)</t>
   </si>
   <si>
     <t xml:space="preserve">nur Vorgabewert 0x021C = 540</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">0x405D</t>
   </si>
   <si>
-    <t xml:space="preserve">Entladeschlussspannung?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nur Vorgabewert 0x01D8 = 470</t>
+    <t xml:space="preserve">Entladeschlussspannung (0x01CC=46,0V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vorgabewerte 0x01D8 = 472 und 0x01C7 = 455</t>
   </si>
   <si>
     <t xml:space="preserve">0x405E</t>
@@ -598,6 +598,12 @@
   </si>
   <si>
     <t xml:space="preserve">0x4066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CosPhi (0x03DB=0,987CosPhi; 0x3E8=1,000CosPhi)</t>
   </si>
   <si>
     <t xml:space="preserve">3x nach
@@ -769,7 +775,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -927,6 +933,12 @@
       <u val="single"/>
       <sz val="11"/>
       <color rgb="FF467886"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1090,7 +1102,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1151,6 +1163,10 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1179,7 +1195,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1295,7 +1311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9663480" cy="17574840"/>
+          <a:ext cx="9661680" cy="17533080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1328,7 +1344,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J130"/>
-  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.13"/>
@@ -3457,7 +3473,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>164</v>
       </c>
@@ -3468,16 +3484,16 @@
         <v>42</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H79" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H79" s="15" t="s">
         <v>165</v>
       </c>
       <c r="I79" s="11" t="s">
@@ -3487,7 +3503,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>167</v>
       </c>
@@ -3498,16 +3514,16 @@
         <v>42</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="15" t="s">
         <v>168</v>
       </c>
       <c r="I80" s="11" t="s">
@@ -3679,7 +3695,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>180</v>
       </c>
@@ -3690,23 +3706,23 @@
         <v>42</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="2"/>
-      <c r="G87" s="2" t="s">
-        <v>16</v>
+      <c r="G87" s="2" t="n">
+        <v>0.001</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>16</v>
+        <v>182</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3723,7 +3739,7 @@
     </row>
     <row r="89" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>41</v>
@@ -3748,12 +3764,12 @@
         <v>39</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>41</v>
@@ -3795,7 +3811,7 @@
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>11</v>
@@ -3814,18 +3830,18 @@
         <v>14</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>11</v>
@@ -3844,18 +3860,18 @@
         <v>14</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>11</v>
@@ -3874,18 +3890,18 @@
         <v>14</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I94" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J94" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>11</v>
@@ -3904,18 +3920,18 @@
         <v>14</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>11</v>
@@ -3931,10 +3947,10 @@
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>46</v>
@@ -3943,7 +3959,7 @@
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>11</v>
@@ -3959,21 +3975,21 @@
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>11</v>
@@ -3989,21 +4005,21 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I98" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J98" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>11</v>
@@ -4019,21 +4035,21 @@
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J99" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I99" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J99" s="13" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>11</v>
@@ -4052,7 +4068,7 @@
         <v>90</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I100" s="12" t="s">
         <v>46</v>
@@ -4061,7 +4077,7 @@
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>11</v>
@@ -4080,18 +4096,18 @@
         <v>90</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I101" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J101" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>11</v>
@@ -4110,18 +4126,18 @@
         <v>90</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I102" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J102" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>11</v>
@@ -4140,18 +4156,18 @@
         <v>90</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>11</v>
@@ -4167,10 +4183,10 @@
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I104" s="12" t="s">
         <v>46</v>
@@ -4179,7 +4195,7 @@
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>11</v>
@@ -4195,21 +4211,21 @@
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I105" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>11</v>
@@ -4225,21 +4241,21 @@
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I106" s="12" t="s">
         <v>46</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>11</v>
@@ -4255,16 +4271,16 @@
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J107" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I107" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="J107" s="13" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,7 +4297,7 @@
     </row>
     <row r="109" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>41</v>
@@ -4306,7 +4322,7 @@
         <v>174</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4323,7 +4339,7 @@
     </row>
     <row r="111" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>41</v>
@@ -4345,10 +4361,10 @@
         <v>16</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,7 +4381,7 @@
     </row>
     <row r="113" customFormat="false" ht="28.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>11</v>
@@ -4374,22 +4390,22 @@
         <v>12</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G113" s="4"/>
-      <c r="H113" s="15" t="s">
-        <v>229</v>
+      <c r="H113" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="I113" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="J113" s="16"/>
+      <c r="J113" s="17"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="11"/>
@@ -4399,13 +4415,13 @@
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
-      <c r="H114" s="16"/>
+      <c r="H114" s="17"/>
       <c r="I114" s="11"/>
-      <c r="J114" s="16"/>
+      <c r="J114" s="17"/>
     </row>
     <row r="115" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="17" t="s">
-        <v>230</v>
+      <c r="A115" s="18" t="s">
+        <v>232</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>11</v>
@@ -4413,177 +4429,177 @@
       <c r="C115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D115" s="18" t="s">
+      <c r="D115" s="19" t="s">
         <v>13</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F115" s="4"/>
-      <c r="G115" s="18" t="s">
+      <c r="G115" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H115" s="19" t="s">
-        <v>231</v>
+      <c r="H115" s="20" t="s">
+        <v>233</v>
       </c>
       <c r="I115" s="11"/>
-      <c r="J115" s="20" t="s">
-        <v>232</v>
+      <c r="J115" s="21" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="21"/>
-      <c r="B116" s="21"/>
-      <c r="C116" s="21"/>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="21"/>
-      <c r="G116" s="21"/>
-      <c r="H116" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="I116" s="21"/>
-      <c r="J116" s="16"/>
+      <c r="A116" s="22"/>
+      <c r="B116" s="22"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22"/>
+      <c r="H116" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="I116" s="22"/>
+      <c r="J116" s="17"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="21"/>
-      <c r="B117" s="21"/>
-      <c r="C117" s="21"/>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="21"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
+      <c r="A117" s="22"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="21"/>
-      <c r="B118" s="21"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="21"/>
-      <c r="G118" s="21"/>
-      <c r="H118" s="21"/>
+      <c r="A118" s="22"/>
+      <c r="B118" s="22"/>
+      <c r="C118" s="22"/>
+      <c r="D118" s="22"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="21"/>
-      <c r="B119" s="21"/>
-      <c r="C119" s="21"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="21"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="21"/>
+      <c r="A119" s="22"/>
+      <c r="B119" s="22"/>
+      <c r="C119" s="22"/>
+      <c r="D119" s="22"/>
+      <c r="E119" s="22"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="22"/>
+      <c r="H119" s="22"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="21"/>
-      <c r="B120" s="21"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="21"/>
-      <c r="G120" s="21"/>
-      <c r="H120" s="21"/>
+      <c r="A120" s="22"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="22"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="22"/>
+      <c r="H120" s="22"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="21"/>
-      <c r="B121" s="21"/>
-      <c r="C121" s="21"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="21"/>
-      <c r="G121" s="21"/>
-      <c r="H121" s="21"/>
+      <c r="A121" s="22"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="22"/>
+      <c r="H121" s="22"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="21"/>
-      <c r="B122" s="21"/>
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="21"/>
-      <c r="G122" s="21"/>
-      <c r="H122" s="21"/>
+      <c r="A122" s="22"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="22"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="21"/>
-      <c r="B123" s="21"/>
-      <c r="C123" s="21"/>
-      <c r="D123" s="21"/>
-      <c r="E123" s="21"/>
-      <c r="F123" s="21"/>
-      <c r="G123" s="21"/>
-      <c r="H123" s="21"/>
+      <c r="A123" s="22"/>
+      <c r="B123" s="22"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="21"/>
-      <c r="B124" s="21"/>
-      <c r="C124" s="21"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="21"/>
-      <c r="G124" s="21"/>
-      <c r="H124" s="21"/>
+      <c r="A124" s="22"/>
+      <c r="B124" s="22"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="22"/>
+      <c r="H124" s="22"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="21"/>
-      <c r="B125" s="21"/>
-      <c r="C125" s="21"/>
-      <c r="D125" s="21"/>
-      <c r="E125" s="21"/>
-      <c r="F125" s="21"/>
-      <c r="G125" s="21"/>
-      <c r="H125" s="21"/>
+      <c r="A125" s="22"/>
+      <c r="B125" s="22"/>
+      <c r="C125" s="22"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="21"/>
-      <c r="B126" s="21"/>
-      <c r="C126" s="21"/>
-      <c r="D126" s="21"/>
-      <c r="E126" s="21"/>
-      <c r="F126" s="21"/>
-      <c r="G126" s="21"/>
-      <c r="H126" s="21"/>
+      <c r="A126" s="22"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
+      <c r="H126" s="22"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="21"/>
-      <c r="B127" s="21"/>
-      <c r="C127" s="21"/>
-      <c r="D127" s="21"/>
-      <c r="E127" s="21"/>
-      <c r="F127" s="21"/>
-      <c r="G127" s="21"/>
-      <c r="H127" s="21"/>
+      <c r="A127" s="22"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="21"/>
-      <c r="B128" s="21"/>
-      <c r="C128" s="21"/>
-      <c r="D128" s="21"/>
-      <c r="E128" s="21"/>
-      <c r="F128" s="21"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="21"/>
+      <c r="A128" s="22"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="21"/>
-      <c r="B129" s="21"/>
-      <c r="C129" s="21"/>
-      <c r="D129" s="21"/>
-      <c r="E129" s="21"/>
-      <c r="F129" s="21"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="21"/>
+      <c r="A129" s="22"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="21"/>
-      <c r="B130" s="21"/>
-      <c r="C130" s="21"/>
-      <c r="D130" s="21"/>
-      <c r="E130" s="21"/>
-      <c r="F130" s="21"/>
-      <c r="G130" s="21"/>
-      <c r="H130" s="21"/>
+      <c r="A130" s="22"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
